--- a/output/pdf_financials_xlsx/AFN.xlsx
+++ b/output/pdf_financials_xlsx/AFN.xlsx
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>13.003</v>
+        <v>29.474</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>13.831</v>
+        <v>33.031</v>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>30.555</v>
+        <v>68.705</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>30.3</v>
+        <v>70.117</v>
       </c>
     </row>
     <row r="29">
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>95.399</v>
+        <v>111.87</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>79.01300000000001</v>
+        <v>98.21299999999999</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>25.229</v>
+        <v>63.379</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>28.451</v>
+        <v>68.268</v>
       </c>
     </row>
     <row r="30">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>43.6181497297841</v>
+        <v>51.14898909077608</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>29.46498159673925</v>
+        <v>36.62491283156635</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>5.631586348832901</v>
+        <v>14.14738242509336</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>7.476166451192466</v>
+        <v>17.93901554567528</v>
       </c>
     </row>
     <row r="31">
@@ -5329,22 +5329,22 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>21.984</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>29.474</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>33.031</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>48.188</v>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
@@ -5352,16 +5352,16 @@
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>40.233</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>27.13</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>68.705</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>70.117</v>
       </c>
     </row>
     <row r="101">
@@ -23309,7 +23309,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -23368,7 +23372,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -23437,7 +23445,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -27214,7 +27222,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -39833,7 +39841,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E474" s="5" t="n">

--- a/output/pdf_financials_xlsx/AFN.xlsx
+++ b/output/pdf_financials_xlsx/AFN.xlsx
@@ -3405,12 +3405,10 @@
         <v>0</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>170.262</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>227.45</v>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
@@ -3624,25 +3622,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G64" s="3" t="n">
+        <v>51.753</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>100.7</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>112.504</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>121.608</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>148.243</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>142.204</v>
       </c>
     </row>
     <row r="65">
@@ -3822,13 +3818,13 @@
         </is>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>100.7</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>112.504</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>121.608</v>
       </c>
       <c r="K68" s="3" t="n">
         <v>264.337</v>
@@ -4154,7 +4150,7 @@
         </is>
       </c>
       <c r="H75" s="3" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0</v>
@@ -5629,16 +5625,16 @@
         <v>0</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>-0.055</v>
+        <v>6.836</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>8.057</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>8.004</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>5.968</v>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
@@ -5646,16 +5642,16 @@
         </is>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>15.62</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>12.159</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>13.758</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>7.418</v>
       </c>
     </row>
     <row r="108">
@@ -5671,10 +5667,10 @@
         <v>0</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0</v>
+        <v>7.839</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0</v>
+        <v>1.932</v>
       </c>
       <c r="F108" s="3" t="n">
         <v>0</v>
@@ -5694,10 +5690,10 @@
         <v>0</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>0</v>
+        <v>2.944</v>
       </c>
       <c r="L108" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="109">
@@ -6007,16 +6003,16 @@
         <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-2.938</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-4.91</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-7.397</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-13.257</v>
       </c>
       <c r="H116" s="1" t="inlineStr">
         <is>
@@ -6024,16 +6020,16 @@
         </is>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-19.017</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-13.655</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-8.625999999999999</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-10.858</v>
       </c>
     </row>
     <row r="117">
@@ -23849,7 +23845,11 @@
           <t>Impairment charge</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -24180,7 +24180,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -25635,7 +25639,11 @@
           <t>Development and acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -27019,7 +27027,11 @@
           <t>Add (deduct) items not affecting cash Development and acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -27882,7 +27894,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -32251,7 +32267,11 @@
           <t>Development and purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -33446,7 +33466,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -34367,7 +34391,11 @@
           <t>Gain on disposal of asset held for sale [note 15] (8) (955) Development and purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -34643,7 +34671,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -37743,7 +37775,11 @@
           <t>Common share issuance, net of issuance costs 60,436 —Development and purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E444" t="inlineStr">
         <is>
           <t>-</t>
